--- a/data/trans_orig/P3A_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471557</t>
+          <t>472374</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486128</t>
+          <t>486606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453305</t>
+          <t>453205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463099</t>
+          <t>463867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>930023</t>
+          <t>929748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>946385</t>
+          <t>947459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>35056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48328</t>
+          <t>47113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701745</t>
+          <t>700433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>720848</t>
+          <t>720001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604105</t>
+          <t>603420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>617599</t>
+          <t>616959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309979</t>
+          <t>1311194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1333194</t>
+          <t>1335113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23207</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36357</t>
+          <t>37675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64522</t>
+          <t>66464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590233</t>
+          <t>589948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614579</t>
+          <t>613400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>663956</t>
+          <t>664445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>679835</t>
+          <t>679598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1263008</t>
+          <t>1261066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291173</t>
+          <t>1289855</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20177</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42807</t>
+          <t>43687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488271</t>
+          <t>488395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>506850</t>
+          <t>507032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497021</t>
+          <t>497087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510613</t>
+          <t>510938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>991982</t>
+          <t>991102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014612</t>
+          <t>1015014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363650</t>
+          <t>362648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379315</t>
+          <t>379201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387644</t>
+          <t>387367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399057</t>
+          <t>398962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>757232</t>
+          <t>756387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>776454</t>
+          <t>775558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38793</t>
+          <t>39357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276792</t>
+          <t>276943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288351</t>
+          <t>288411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>314041</t>
+          <t>315228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330535</t>
+          <t>330937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>596724</t>
+          <t>596160</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>617874</t>
+          <t>616737</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>27648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>24313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>48517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41804</t>
+          <t>41811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71926</t>
+          <t>70223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>181836</t>
+          <t>182235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197519</t>
+          <t>197328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285244</t>
+          <t>285391</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309035</t>
+          <t>309595</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>471865</t>
+          <t>473568</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>501987</t>
+          <t>501980</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110225</t>
+          <t>111528</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156128</t>
+          <t>161196</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87566</t>
+          <t>86206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128710</t>
+          <t>126266</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211408</t>
+          <t>209386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271328</t>
+          <t>269777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3119533</t>
+          <t>3114465</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3165436</t>
+          <t>3164133</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3245935</t>
+          <t>3248379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3287079</t>
+          <t>3288439</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6378979</t>
+          <t>6380530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6438899</t>
+          <t>6440921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19069</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435077</t>
+          <t>435056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449082</t>
+          <t>448258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414848</t>
+          <t>414439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427335</t>
+          <t>427383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>856094</t>
+          <t>855873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873420</t>
+          <t>873042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>663721</t>
+          <t>665672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>680347</t>
+          <t>680339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>592467</t>
+          <t>592366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605279</t>
+          <t>605253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1262546</t>
+          <t>1262599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1282893</t>
+          <t>1282251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26943</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28744</t>
+          <t>27744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49229</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>654920</t>
+          <t>653689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673239</t>
+          <t>672252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>681104</t>
+          <t>682104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>699555</t>
+          <t>699379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1342482</t>
+          <t>1345137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1369373</t>
+          <t>1369271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27318</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22733</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>46964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>587299</t>
+          <t>586447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>605105</t>
+          <t>605034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588200</t>
+          <t>588580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607103</t>
+          <t>606910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1182386</t>
+          <t>1183852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1208083</t>
+          <t>1208375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407865</t>
+          <t>406870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422116</t>
+          <t>421217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417418</t>
+          <t>419269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>436499</t>
+          <t>436745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830566</t>
+          <t>831335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>854409</t>
+          <t>854624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>26747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24365</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>47651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280587</t>
+          <t>279453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298438</t>
+          <t>298408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326628</t>
+          <t>326250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>343241</t>
+          <t>342669</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>614319</t>
+          <t>615132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>638418</t>
+          <t>637788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31390</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55752</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59552</t>
+          <t>58983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>92136</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98744</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139676</t>
+          <t>139168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194099</t>
+          <t>194021</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218461</t>
+          <t>219264</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296713</t>
+          <t>296843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>329427</t>
+          <t>329996</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>499154</t>
+          <t>499662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>540086</t>
+          <t>539747</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>107120</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>154617</t>
+          <t>156295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>139713</t>
+          <t>135629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192863</t>
+          <t>188487</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>260008</t>
+          <t>261714</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>327290</t>
+          <t>328811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3271102</t>
+          <t>3269424</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3317986</t>
+          <t>3318599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3363445</t>
+          <t>3367821</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3416595</t>
+          <t>3420679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6654737</t>
+          <t>6653216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6722019</t>
+          <t>6720313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404153</t>
+          <t>403208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414676</t>
+          <t>414561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386821</t>
+          <t>385994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394731</t>
+          <t>394754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794677</t>
+          <t>795094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>807653</t>
+          <t>807505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>580996</t>
+          <t>582503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548305</t>
+          <t>547400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559675</t>
+          <t>559605</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134737</t>
+          <t>1134744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1148160</t>
+          <t>1148137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653367</t>
+          <t>653438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663601</t>
+          <t>663591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645162</t>
+          <t>645595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657809</t>
+          <t>657842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303260</t>
+          <t>1304075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319111</t>
+          <t>1319369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>628691</t>
+          <t>628814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640394</t>
+          <t>640442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632674</t>
+          <t>632817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644101</t>
+          <t>643995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266271</t>
+          <t>1265382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1283105</t>
+          <t>1283000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>38945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>446280</t>
+          <t>447889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467650</t>
+          <t>467405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>481203</t>
+          <t>482995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492397</t>
+          <t>493514</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>934912</t>
+          <t>934719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957051</t>
+          <t>957773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>321148</t>
+          <t>321872</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331212</t>
+          <t>331306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>353285</t>
+          <t>352295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368310</t>
+          <t>368101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>679789</t>
+          <t>679714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>698527</t>
+          <t>698478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>26338</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47524</t>
+          <t>47271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44499</t>
+          <t>43707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78157</t>
+          <t>78197</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75027</t>
+          <t>77516</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114279</t>
+          <t>116073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208738</t>
+          <t>208991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>229630</t>
+          <t>229924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>322012</t>
+          <t>321972</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355670</t>
+          <t>356462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>542152</t>
+          <t>540358</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>581404</t>
+          <t>578915</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66300</t>
+          <t>64369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101792</t>
+          <t>100996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>87941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>132776</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162745</t>
+          <t>158996</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220265</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3283517</t>
+          <t>3284313</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3319009</t>
+          <t>3320940</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3407457</t>
+          <t>3406804</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3454645</t>
+          <t>3451639</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6704625</t>
+          <t>6706099</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6762145</t>
+          <t>6765894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27008</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372979</t>
+          <t>370897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397285</t>
+          <t>397317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300386</t>
+          <t>298880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311670</t>
+          <t>311654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676920</t>
+          <t>678528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705134</t>
+          <t>705634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407219</t>
+          <t>407317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501496</t>
+          <t>501757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511117</t>
+          <t>511146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>917030</t>
+          <t>916010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933613</t>
+          <t>933998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517843</t>
+          <t>517696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531565</t>
+          <t>531375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>580188</t>
+          <t>579914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>589014</t>
+          <t>588857</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1103891</t>
+          <t>1102576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1119016</t>
+          <t>1118887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52546</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856106</t>
+          <t>856825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880604</t>
+          <t>880629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>683101</t>
+          <t>684069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698599</t>
+          <t>698778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1547427</t>
+          <t>1546480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1577344</t>
+          <t>1577683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28360</t>
+          <t>28726</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45170</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532874</t>
+          <t>532508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>549119</t>
+          <t>549116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526398</t>
+          <t>525839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>538283</t>
+          <t>538587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1063969</t>
+          <t>1064500</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1084796</t>
+          <t>1084397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32780</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47967</t>
+          <t>48159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73357</t>
+          <t>73807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>334286</t>
+          <t>334700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>349756</t>
+          <t>349217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>559835</t>
+          <t>559643</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>597030</t>
+          <t>598346</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>901512</t>
+          <t>901062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947436</t>
+          <t>948398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52437</t>
+          <t>52214</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74415</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106849</t>
+          <t>106890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133273</t>
+          <t>132502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164623</t>
+          <t>164940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197970</t>
+          <t>199188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208344</t>
+          <t>207838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230322</t>
+          <t>230545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>292558</t>
+          <t>293329</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318982</t>
+          <t>318941</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>510620</t>
+          <t>509402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>543967</t>
+          <t>543650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>115754</t>
+          <t>115599</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179417</t>
+          <t>174998</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165465</t>
+          <t>157053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223279</t>
+          <t>225152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>303718</t>
+          <t>299741</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>390597</t>
+          <t>389766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3279301</t>
+          <t>3283720</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3342964</t>
+          <t>3343119</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3487741</t>
+          <t>3485868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3545555</t>
+          <t>3553967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6779141</t>
+          <t>6779972</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6866020</t>
+          <t>6869997</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>22518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>472374</t>
+          <t>471546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486606</t>
+          <t>485929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453205</t>
+          <t>453171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463867</t>
+          <t>463113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>929748</t>
+          <t>929318</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947459</t>
+          <t>947352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>34424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>19550</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47113</t>
+          <t>48396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>700433</t>
+          <t>701065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>720001</t>
+          <t>719719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>603420</t>
+          <t>603269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>616959</t>
+          <t>616863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1309911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1335113</t>
+          <t>1333883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>23656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47838</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37675</t>
+          <t>37712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66464</t>
+          <t>66192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>589948</t>
+          <t>589796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613400</t>
+          <t>614130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664445</t>
+          <t>663673</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>679598</t>
+          <t>679665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1261066</t>
+          <t>1261338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289855</t>
+          <t>1289818</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30752</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43687</t>
+          <t>42338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488395</t>
+          <t>487374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507032</t>
+          <t>507088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497087</t>
+          <t>497465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510938</t>
+          <t>510612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>991102</t>
+          <t>992451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015014</t>
+          <t>1014526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>362648</t>
+          <t>362751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379201</t>
+          <t>379276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387367</t>
+          <t>387504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>398962</t>
+          <t>399256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>756387</t>
+          <t>757773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>775558</t>
+          <t>776442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>19789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39357</t>
+          <t>40445</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276943</t>
+          <t>275961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288411</t>
+          <t>288386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315228</t>
+          <t>315706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330937</t>
+          <t>331537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>596160</t>
+          <t>595072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>616737</t>
+          <t>615728</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27648</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24313</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48517</t>
+          <t>46937</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41811</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70223</t>
+          <t>68481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182235</t>
+          <t>181362</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197328</t>
+          <t>197455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285391</t>
+          <t>286971</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309595</t>
+          <t>309395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>473568</t>
+          <t>475310</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>501980</t>
+          <t>503086</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111528</t>
+          <t>111755</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161196</t>
+          <t>157176</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>86834</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126266</t>
+          <t>128260</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>209386</t>
+          <t>211271</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269777</t>
+          <t>270028</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3114465</t>
+          <t>3118485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3164133</t>
+          <t>3163906</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3248379</t>
+          <t>3246385</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3288439</t>
+          <t>3287811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6380530</t>
+          <t>6380279</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6440921</t>
+          <t>6439036</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435056</t>
+          <t>435994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448258</t>
+          <t>448234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414439</t>
+          <t>414712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427383</t>
+          <t>427422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>855873</t>
+          <t>855956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873042</t>
+          <t>873470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15091</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34743</t>
+          <t>33610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665672</t>
+          <t>664954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>680339</t>
+          <t>680440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>592366</t>
+          <t>590566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605253</t>
+          <t>604845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1262599</t>
+          <t>1263732</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1282251</t>
+          <t>1282568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46574</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653689</t>
+          <t>654252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>672252</t>
+          <t>673271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682104</t>
+          <t>681325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>699379</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1345137</t>
+          <t>1343366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1369271</t>
+          <t>1368738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>28907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46964</t>
+          <t>48481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>586447</t>
+          <t>587189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>605034</t>
+          <t>605274</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588580</t>
+          <t>587292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606910</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183852</t>
+          <t>1182335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1208375</t>
+          <t>1207854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44835</t>
+          <t>44786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406870</t>
+          <t>406955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421217</t>
+          <t>421896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419269</t>
+          <t>418482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>436745</t>
+          <t>436690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>831335</t>
+          <t>831384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>854624</t>
+          <t>854163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>24141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>48050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279453</t>
+          <t>280113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298408</t>
+          <t>298322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326250</t>
+          <t>327002</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342669</t>
+          <t>343976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>615132</t>
+          <t>614733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>637788</t>
+          <t>638642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>32550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55830</t>
+          <t>56429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58983</t>
+          <t>60383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92136</t>
+          <t>93863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99083</t>
+          <t>98679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139168</t>
+          <t>138443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194021</t>
+          <t>193422</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219264</t>
+          <t>217301</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296843</t>
+          <t>295116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>329996</t>
+          <t>328596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>499662</t>
+          <t>500387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>539747</t>
+          <t>540151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107120</t>
+          <t>106620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156295</t>
+          <t>154326</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135629</t>
+          <t>135337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>188487</t>
+          <t>187871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>261714</t>
+          <t>256649</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>328811</t>
+          <t>329203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3269424</t>
+          <t>3271393</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3318599</t>
+          <t>3319099</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3367821</t>
+          <t>3368437</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3420679</t>
+          <t>3420971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6653216</t>
+          <t>6652824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6720313</t>
+          <t>6725378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403208</t>
+          <t>403852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414561</t>
+          <t>414542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385994</t>
+          <t>386632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394754</t>
+          <t>394758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>795094</t>
+          <t>794799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>807505</t>
+          <t>807378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582503</t>
+          <t>582079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>547400</t>
+          <t>548129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559605</t>
+          <t>559806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134744</t>
+          <t>1134221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1148137</t>
+          <t>1148240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653438</t>
+          <t>653572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663591</t>
+          <t>663623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645595</t>
+          <t>645629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657842</t>
+          <t>657850</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1304075</t>
+          <t>1304785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319369</t>
+          <t>1319848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>15277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>628814</t>
+          <t>627781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640442</t>
+          <t>640381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632817</t>
+          <t>632759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643995</t>
+          <t>644168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1265382</t>
+          <t>1266195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1283000</t>
+          <t>1282384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38945</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447889</t>
+          <t>447146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467405</t>
+          <t>467474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>482995</t>
+          <t>480955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>493514</t>
+          <t>492436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>934719</t>
+          <t>935542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957773</t>
+          <t>957294</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30373</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>321872</t>
+          <t>322192</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331306</t>
+          <t>331320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>352295</t>
+          <t>353264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368101</t>
+          <t>368341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>679714</t>
+          <t>678667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>698478</t>
+          <t>697319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>25808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47271</t>
+          <t>46865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43707</t>
+          <t>43378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78197</t>
+          <t>76499</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77516</t>
+          <t>75697</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116073</t>
+          <t>115180</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208991</t>
+          <t>209397</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>229924</t>
+          <t>230454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321972</t>
+          <t>323670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356462</t>
+          <t>356791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>540358</t>
+          <t>541251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578915</t>
+          <t>580734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,47%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>66300</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100996</t>
+          <t>100802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87941</t>
+          <t>87896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132776</t>
+          <t>132928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158996</t>
+          <t>162606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218791</t>
+          <t>221779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3284313</t>
+          <t>3284507</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3320940</t>
+          <t>3319009</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3406804</t>
+          <t>3406652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3451639</t>
+          <t>3451684</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6706099</t>
+          <t>6703111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6765894</t>
+          <t>6762284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>29230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,22 +9735,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>34625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>388327</t>
+          <t>396108</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370897</t>
+          <t>378563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397317</t>
+          <t>404946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>307404</t>
+          <t>356934</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298880</t>
+          <t>348381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311654</t>
+          <t>361091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>695730</t>
+          <t>753042</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678528</t>
+          <t>735680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705634</t>
+          <t>762166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420269</t>
+          <t>473015</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407317</t>
+          <t>454265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>508374</t>
+          <t>497738</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501757</t>
+          <t>490529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511146</t>
+          <t>500657</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>928644</t>
+          <t>970753</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916010</t>
+          <t>950449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933998</t>
+          <t>976457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,22 +10351,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526848</t>
+          <t>609969</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517696</t>
+          <t>600794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531375</t>
+          <t>615087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>585847</t>
+          <t>615782</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579914</t>
+          <t>609870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>588857</t>
+          <t>619456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1112695</t>
+          <t>1225751</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1102576</t>
+          <t>1215832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1118887</t>
+          <t>1232616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18562</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>31010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>30974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>54565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>869224</t>
+          <t>679841</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856825</t>
+          <t>669607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880629</t>
+          <t>687998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>692123</t>
+          <t>715128</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>684069</t>
+          <t>708200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698778</t>
+          <t>721691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1561347</t>
+          <t>1394969</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1546480</t>
+          <t>1382262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1577683</t>
+          <t>1405853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,22 +11037,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>35686</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44639</t>
+          <t>48356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -11150,27 +11150,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>542184</t>
+          <t>589367</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532508</t>
+          <t>578791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>549116</t>
+          <t>596180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>533276</t>
+          <t>593149</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>525839</t>
+          <t>586867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>538587</t>
+          <t>598548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1075460</t>
+          <t>1182516</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1064500</t>
+          <t>1169846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1084397</t>
+          <t>1192121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>35568</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>25842</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>60861</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>49469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73807</t>
+          <t>73795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>342474</t>
+          <t>379016</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>334700</t>
+          <t>370418</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>349217</t>
+          <t>387067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>578453</t>
+          <t>404707</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>559643</t>
+          <t>396198</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>598346</t>
+          <t>412756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>920928</t>
+          <t>783723</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>901062</t>
+          <t>770789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>948398</t>
+          <t>795115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>62418</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74921</t>
+          <t>79375</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>119018</t>
+          <t>130695</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106890</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132502</t>
+          <t>145839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>181436</t>
+          <t>197962</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164940</t>
+          <t>179485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>199188</t>
+          <t>217854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>220341</t>
+          <t>242931</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>207838</t>
+          <t>230823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230545</t>
+          <t>254012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>306813</t>
+          <t>333914</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293329</t>
+          <t>318770</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318941</t>
+          <t>347733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>527154</t>
+          <t>576845</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>509402</t>
+          <t>556953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>543650</t>
+          <t>595322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>149050</t>
+          <t>161420</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>115599</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>174998</t>
+          <t>189508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>198729</t>
+          <t>218358</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>157053</t>
+          <t>195052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225152</t>
+          <t>241052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>347779</t>
+          <t>379778</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>299741</t>
+          <t>346329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>389766</t>
+          <t>416088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3309668</t>
+          <t>3370249</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3283720</t>
+          <t>3342161</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3343119</t>
+          <t>3392609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3512291</t>
+          <t>3517351</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3485868</t>
+          <t>3494657</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3553967</t>
+          <t>3540657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6821959</t>
+          <t>6887600</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6779972</t>
+          <t>6851290</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6869997</t>
+          <t>6921049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
